--- a/r4-ELGA-e-Medikation-BO_rework_use_case/ValueSet-MedikationsplaneintragStatusVS.xlsx
+++ b/r4-ELGA-e-Medikation-BO_rework_use_case/ValueSet-MedikationsplaneintragStatusVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T13:59:43+00:00</t>
+    <t>2026-07-27T19:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-BO_rework_use_case/ValueSet-MedikationsplaneintragStatusVS.xlsx
+++ b/r4-ELGA-e-Medikation-BO_rework_use_case/ValueSet-MedikationsplaneintragStatusVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T19:55:21+00:00</t>
+    <t>2026-07-27T20:12:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-BO_rework_use_case/ValueSet-MedikationsplaneintragStatusVS.xlsx
+++ b/r4-ELGA-e-Medikation-BO_rework_use_case/ValueSet-MedikationsplaneintragStatusVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T20:12:18+00:00</t>
+    <t>2026-07-27T22:11:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
